--- a/H2coco/TradeFinance.xlsx
+++ b/H2coco/TradeFinance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leo/Github/XeroAPI/H2coco/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEA6451-0CBD-5441-A298-754F4AFCF018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA163FC3-F2D2-4DB3-B466-9D9DFEB276CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16000" yWindow="-25820" windowWidth="28040" windowHeight="17440" xr2:uid="{FFDF8704-F7A6-5241-858B-D62B61F118F7}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="18810" xr2:uid="{FFDF8704-F7A6-5241-858B-D62B61F118F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -438,12 +438,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E04BC2-FCC1-F344-980C-32A6AB851348}">
   <dimension ref="A1:H71"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="10.83203125" style="5"/>
+    <col min="8" max="8" width="10.875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -457,7 +457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>4582</v>
       </c>
@@ -471,7 +471,7 @@
         <v>14586</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>4598</v>
       </c>
@@ -485,7 +485,7 @@
         <v>14586</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4601</v>
       </c>
@@ -499,7 +499,7 @@
         <v>14586</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4602</v>
       </c>
@@ -513,7 +513,7 @@
         <v>14586</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>4629</v>
       </c>
@@ -527,7 +527,7 @@
         <v>14586</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>4650</v>
       </c>
@@ -541,7 +541,7 @@
         <v>29172</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>4652</v>
       </c>
@@ -555,7 +555,7 @@
         <v>14586</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>4745</v>
       </c>
@@ -569,7 +569,7 @@
         <v>14586</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>4833</v>
       </c>
@@ -583,7 +583,7 @@
         <v>4158</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>4834</v>
       </c>
@@ -597,7 +597,7 @@
         <v>4158</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>4835</v>
       </c>
@@ -611,7 +611,7 @@
         <v>4428</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>4836</v>
       </c>
@@ -625,7 +625,7 @@
         <v>4252.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>4838</v>
       </c>
@@ -639,7 +639,7 @@
         <v>3801.6</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>4392</v>
       </c>
@@ -653,7 +653,7 @@
         <v>11076.8</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>4394</v>
       </c>
@@ -667,7 +667,7 @@
         <v>8870.4</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>4424</v>
       </c>
@@ -681,7 +681,7 @@
         <v>9759.7800000000007</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>4425</v>
       </c>
@@ -695,7 +695,7 @@
         <v>8870.4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>4487</v>
       </c>
@@ -709,7 +709,7 @@
         <v>9064.2999999999993</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>4551</v>
       </c>
@@ -723,7 +723,7 @@
         <v>9601.5499999999993</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>4560</v>
       </c>
@@ -737,7 +737,7 @@
         <v>7739.55</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>4581</v>
       </c>
@@ -751,7 +751,7 @@
         <v>8255.52</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>4584</v>
       </c>
@@ -765,7 +765,7 @@
         <v>7735.05</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>4591</v>
       </c>
@@ -779,7 +779,7 @@
         <v>9601.5499999999993</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>4592</v>
       </c>
@@ -793,7 +793,7 @@
         <v>9072.35</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>4593</v>
       </c>
@@ -807,7 +807,7 @@
         <v>9286.5499999999993</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>4622</v>
       </c>
@@ -821,7 +821,7 @@
         <v>7858.55</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>4624</v>
       </c>
@@ -835,7 +835,7 @@
         <v>9072.35</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>4683</v>
       </c>
@@ -849,7 +849,7 @@
         <v>9702</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>4701</v>
       </c>
@@ -863,7 +863,7 @@
         <v>9526.44</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>4474</v>
       </c>
@@ -877,7 +877,7 @@
         <v>14586</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>4544</v>
       </c>
@@ -891,7 +891,7 @@
         <v>29172</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>4578</v>
       </c>
@@ -905,7 +905,7 @@
         <v>29172</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>4653</v>
       </c>
@@ -919,7 +919,7 @@
         <v>29172</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>4676</v>
       </c>
@@ -933,7 +933,7 @@
         <v>30105</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>4681</v>
       </c>
@@ -947,7 +947,7 @@
         <v>14586</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>4735</v>
       </c>
@@ -961,7 +961,7 @@
         <v>15082.2</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>4742</v>
       </c>
@@ -975,7 +975,7 @@
         <v>15082.2</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>4761</v>
       </c>
@@ -989,7 +989,7 @@
         <v>14586</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>4770</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>14586</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>4771</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>14586</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>4774</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>14586</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>4775</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>14586</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>4778</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>14586</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>4817</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>14586</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>4860</v>
       </c>
@@ -1087,159 +1087,151 @@
         <v>11700</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="2">
-        <v>4861</v>
-      </c>
-      <c r="B47" s="3">
-        <v>46013</v>
-      </c>
-      <c r="C47" s="2">
-        <v>0.65949000000000002</v>
-      </c>
-      <c r="D47" s="4">
-        <v>12168</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="2"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="4"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" s="2"/>
       <c r="D48" s="4"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
       <c r="C49" s="2"/>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="3"/>
       <c r="C50" s="2"/>
       <c r="D50" s="4"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="3"/>
       <c r="C51" s="2"/>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="C52" s="2"/>
       <c r="D52" s="4"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
       <c r="C53" s="2"/>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" s="2"/>
       <c r="D54" s="4"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="C55" s="2"/>
       <c r="D55" s="4"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="C56" s="2"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" s="2"/>
       <c r="D57" s="4"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="C58" s="2"/>
       <c r="D58" s="4"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" s="2"/>
       <c r="D59" s="4"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" s="2"/>
       <c r="D60" s="4"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="2"/>
       <c r="D61" s="4"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" s="2"/>
       <c r="D62" s="4"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="2"/>
       <c r="D63" s="4"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="3"/>
       <c r="C64" s="2"/>
       <c r="D64" s="4"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="2"/>
       <c r="D65" s="4"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" s="2"/>
       <c r="D66" s="4"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="C67" s="2"/>
       <c r="D67" s="4"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="3"/>
       <c r="C68" s="2"/>
       <c r="D68" s="4"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="C69" s="2"/>
       <c r="D69" s="4"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="3"/>
       <c r="C70" s="2"/>
       <c r="D70" s="4"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="C71" s="2"/>
